--- a/2026년 상반기 건강디딤돌 신청 결과.xlsx
+++ b/2026년 상반기 건강디딤돌 신청 결과.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\cursor\측정일지_Html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\cursor\측정일지_html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D018E842-0F89-4EFE-9033-D0A0C8228758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34BBFAD-E992-4AFE-B2C0-2A9B12D7CD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{5B557176-1373-4E89-87BB-14B6567208A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B557176-1373-4E89-87BB-14B6567208A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="1427">
   <si>
     <t>사업장관리번호</t>
   </si>
@@ -4142,6 +4142,234 @@
   </si>
   <si>
     <t>H0276</t>
+  </si>
+  <si>
+    <t>31281545056</t>
+  </si>
+  <si>
+    <t>92508857597</t>
+  </si>
+  <si>
+    <t>(주) 광전사 천안 스마트그린산단 통합관제센터 스마트횡단보도 설치</t>
+  </si>
+  <si>
+    <t>박현석</t>
+  </si>
+  <si>
+    <t>충청남도 천안시 서북구 3공단6로 86-9 제3일반산업단지 일대 (차암동)</t>
+  </si>
+  <si>
+    <t>정동주</t>
+  </si>
+  <si>
+    <t>88837115</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>결과 없음</t>
+  </si>
+  <si>
+    <t>H0407</t>
+  </si>
+  <si>
+    <t>91201346717</t>
+  </si>
+  <si>
+    <t>92511385327</t>
+  </si>
+  <si>
+    <t>남영물류산업 (주) SEN2 FC Fresh Mezzanine 설치 공사</t>
+  </si>
+  <si>
+    <t>남후식</t>
+  </si>
+  <si>
+    <t>표석원</t>
+  </si>
+  <si>
+    <t>87948196</t>
+  </si>
+  <si>
+    <t>H0413</t>
+  </si>
+  <si>
+    <t>92513204647</t>
+  </si>
+  <si>
+    <t>남영물류산업 (주) 쿠팡 CHA6 FC Mezzanine 설치 공사</t>
+  </si>
+  <si>
+    <t>전윤철</t>
+  </si>
+  <si>
+    <t>26525861</t>
+  </si>
+  <si>
+    <t>비대상</t>
+  </si>
+  <si>
+    <t>H0422</t>
+  </si>
+  <si>
+    <t>92507715147</t>
+  </si>
+  <si>
+    <t>남영물류산업 (주) 쿠팡 CHA8 B2F Mezzanine 제작 및 설치공사</t>
+  </si>
+  <si>
+    <t>충청남도 천안시 서북구 성환읍 대홍4길 15-5 (대홍리)</t>
+  </si>
+  <si>
+    <t>김태선</t>
+  </si>
+  <si>
+    <t>83148999</t>
+  </si>
+  <si>
+    <t>H0409</t>
+  </si>
+  <si>
+    <t>50581089616</t>
+  </si>
+  <si>
+    <t>92409023477</t>
+  </si>
+  <si>
+    <t>우석종합건설(주) 천안천 풍수해생활권 종합정비사업</t>
+  </si>
+  <si>
+    <t>손동우</t>
+  </si>
+  <si>
+    <t>충청남도 천안시 서북구 와촌동 130</t>
+  </si>
+  <si>
+    <t>김장호</t>
+  </si>
+  <si>
+    <t>36275938</t>
+  </si>
+  <si>
+    <t>근로자수 51인</t>
+  </si>
+  <si>
+    <t>H0366</t>
+  </si>
+  <si>
+    <t>17386004286</t>
+  </si>
+  <si>
+    <t>92500085077</t>
+  </si>
+  <si>
+    <t>은성건설 주식회사 (주)디에스테크노 문막공장 신축공사</t>
+  </si>
+  <si>
+    <t>이동준</t>
+  </si>
+  <si>
+    <t>강원특별자치도 원주시 문막읍 문막공단길 202 (반계리)</t>
+  </si>
+  <si>
+    <t>김인성</t>
+  </si>
+  <si>
+    <t>65154438</t>
+  </si>
+  <si>
+    <t>근로자수 50인</t>
+  </si>
+  <si>
+    <t>H0344</t>
+  </si>
+  <si>
+    <t>12681574300</t>
+  </si>
+  <si>
+    <t>일신산업전기 (주)</t>
+  </si>
+  <si>
+    <t>고수영</t>
+  </si>
+  <si>
+    <t>경기도 광주시 광주대로 200-1 (송정동)</t>
+  </si>
+  <si>
+    <t>신민재</t>
+  </si>
+  <si>
+    <t>23612820</t>
+  </si>
+  <si>
+    <t>H0396</t>
+  </si>
+  <si>
+    <t>45581003300</t>
+  </si>
+  <si>
+    <t>주식회사 에스케이팩</t>
+  </si>
+  <si>
+    <t>이익희</t>
+  </si>
+  <si>
+    <t>경기도 광주시 초월읍 현산로361번길 13-8 (지월리)</t>
+  </si>
+  <si>
+    <t>박준수</t>
+  </si>
+  <si>
+    <t>99898913</t>
+  </si>
+  <si>
+    <t>H0349</t>
+  </si>
+  <si>
+    <t>88188012360</t>
+  </si>
+  <si>
+    <t>주식회사 아이엘사이언스</t>
+  </si>
+  <si>
+    <t>송성근</t>
+  </si>
+  <si>
+    <t>충청남도 천안시 동남구 수신면 장산동길 32 (장산리)</t>
+  </si>
+  <si>
+    <t>이강덕</t>
+  </si>
+  <si>
+    <t>34321892</t>
+  </si>
+  <si>
+    <t>근로자수 50인 이상</t>
+  </si>
+  <si>
+    <t>H0110</t>
+  </si>
+  <si>
+    <t>92514521447</t>
+  </si>
+  <si>
+    <t>남영건설 (주) 쿠팡 INC43 Ph2 Mezzanine 설치 공사</t>
+  </si>
+  <si>
+    <t>인천 서구 봉수대로 370</t>
+  </si>
+  <si>
+    <t>마민제</t>
+  </si>
+  <si>
+    <t>55600835</t>
+  </si>
+  <si>
+    <t>근로자수 52인</t>
+  </si>
+  <si>
+    <t>H0432</t>
   </si>
 </sst>
 </file>
@@ -4631,7 +4859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9771CBA8-E1B1-4125-9446-F4371A5311D4}">
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J218"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
@@ -11297,6 +11525,326 @@
         <v>1350</v>
       </c>
     </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E209" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G209" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H209" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I209" t="s">
+        <v>1359</v>
+      </c>
+      <c r="J209" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E210" t="s">
+        <v>779</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G210" t="s">
+        <v>1366</v>
+      </c>
+      <c r="H210" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I210" t="s">
+        <v>1359</v>
+      </c>
+      <c r="J210" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E211" t="s">
+        <v>419</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G211" t="s">
+        <v>1371</v>
+      </c>
+      <c r="H211" t="s">
+        <v>17</v>
+      </c>
+      <c r="I211" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J211" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E212" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G212" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H212" t="s">
+        <v>17</v>
+      </c>
+      <c r="I212" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J212" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E213" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G213" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H213" t="s">
+        <v>1387</v>
+      </c>
+      <c r="I213" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J213" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G214" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I214" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J214" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G215" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I215" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J215" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B216" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G216" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H216" t="s">
+        <v>1387</v>
+      </c>
+      <c r="I216" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J216" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E217" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G217" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1418</v>
+      </c>
+      <c r="I217" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J217" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G218" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H218" t="s">
+        <v>1425</v>
+      </c>
+      <c r="I218" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J218" t="s">
+        <v>1426</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
